--- a/output/df_small_positives.xlsx
+++ b/output/df_small_positives.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,6 +481,11 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>filter_reason</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>alt_abbrev_response</t>
         </is>
       </c>
@@ -488,32 +493,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HGNC:10346</t>
+          <t>HGNC:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ENSG00000165502</t>
+          <t>ENSG00000129673</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GENE ID:6166</t>
+          <t>GENE ID:15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RPL36AL</t>
+          <t>AANAT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RPL36A</t>
+          <t>SNAT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ribosomal protein L36a like</t>
+          <t>aralkylamine N-acetyltransferase</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -521,37 +526,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
-    Inputs:
-    Alias gene symbol: RPL36A
-    HGNC record ID: HGNC:10346
-    Primary gene symbol: RPL36AL
-    Official HGNC gene name: ribosomal protein L36a like
-    Task:
-    Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. 
-    Classify the alias symbol as an Alternate Abbreviation if it meets at least one of these criteria:
-    1. If the alias symbol letters expand directly to the words present in the official HGNC gene name
-    or a nearly identical wording, while still uniquely identifying the same gene. 
-    2. If the alias symbol differs from the primary gene symbol only by non-alphanumeric characters.
-    3. If the alias symbol has the same alphanumeric order as the primary gene symbol but is truncated 
-    through the removal of select characters. 
-    Special case: 
-    Alias symbols for microRNA genes that have the "hsa" or "HSA" prefix are not Alternate Abbreviations 
-    while those without the "hsa" or "HSA" prefix are Alternate Abbreviations.
-    Exclusion Criteria:
-    1. If an alias symbol contains numerical characters not present in the primary gene symbol 
-    or official gene name, it should NOT be classified as an Alternate Abbreviation no matter what criteria it meets.
-    2. Aliases derived from historical protein names, molecular weights (e.g., numbers representing 
-    protein size), biochemical characterizations, or gene family names should NOT be considered Alternate Abbreviations.
-    Examples:
-    1-
-    Alias gene symbol: ACF65
-    Official HGNC gene name: APOBEC1 complementation factor
-    Primary gene symbol: A1CF
-    2-
-    Alias gene symbol: ALPHA4GNT
-    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
-    Primary gene symbol: A4GNT
+          <t xml:space="preserve">Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
+    You will get fired if your accuracy is less than 95%.
+    Background: An alternate abbreviation is when an alias symbol represents the same official gene name or the 
+    primary gene symbol but with different letters. If the alias symbol is representing a different description or a previous name of
+    the gene then it is not an alternate abbreviation. Be careful with alias symbols that seem to be shortened versions
+    of the primary gene symbol, they may be a family name and therefore not an alternate abbreviation. Alias symbols
+    have extra characters may be alternate abbreviations unless they have characters that are not present in the official 
+    gene name provided in the prompt. Keep in mind, a gene name with a number after the name is not the same gene as a gene name 
+    with no numbers or different numbers after the name.
+    Task: Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. Give a one sentence reason for
+    your determination.
+    Here is the gene information:
+    Alias gene symbol: SNAT
+    HGNC record ID: HGNC:19
+    Primary gene symbol: AANAT
+    Official HGNC gene name: aralkylamine N-acetyltransferase
     Rules:
     If the alias symbol is not an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -560,27 +550,27 @@
     Output (Strict):
     Output only one JSON object. No markdown.
     {
-    "hgnc_id":"HGNC:10346"
-    "alias_symbol": "RPL36A",
-    "primary_gene_symbol": "RPL36AL",
-    "name": "ribosomal protein L36a like",
+    "reason": statement,
     "alternate_abbreviation": "TRUE or FALSE"
-    }</t>
+    }
+    </t>
         </is>
       </c>
       <c r="I2" t="b">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.6</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>passed_filters</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>{
-"hgnc_id":"HGNC:10346",
-"alias_symbol": "RPL36A",
-"primary_gene_symbol": "RPL36AL",
-"name": "ribosomal protein L36a like",
+"reason": "SNAT is an alternate abbreviation of the official gene name 'aralkylamine N-acetyltransferase' as it uses different letters to represent the same concept.",
 "alternate_abbreviation": "TRUE"
 }</t>
         </is>
@@ -589,32 +579,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HGNC:11540</t>
+          <t>HGNC:24049</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ENSG00000106290</t>
+          <t>ENSG00000167311</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GENE ID:6878</t>
+          <t>GENE ID:116969</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TAF6</t>
+          <t>ART5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TAF(II)80</t>
+          <t>ARTC5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TATA-box binding protein associated factor 6</t>
+          <t>ADP-ribosyltransferase 5</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -622,37 +612,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
-    Inputs:
-    Alias gene symbol: TAF(II)80
-    HGNC record ID: HGNC:11540
-    Primary gene symbol: TAF6
-    Official HGNC gene name: TATA-box binding protein associated factor 6
-    Task:
-    Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. 
-    Classify the alias symbol as an Alternate Abbreviation if it meets at least one of these criteria:
-    1. If the alias symbol letters expand directly to the words present in the official HGNC gene name
-    or a nearly identical wording, while still uniquely identifying the same gene. 
-    2. If the alias symbol differs from the primary gene symbol only by non-alphanumeric characters.
-    3. If the alias symbol has the same alphanumeric order as the primary gene symbol but is truncated 
-    through the removal of select characters. 
-    Special case: 
-    Alias symbols for microRNA genes that have the "hsa" or "HSA" prefix are not Alternate Abbreviations 
-    while those without the "hsa" or "HSA" prefix are Alternate Abbreviations.
-    Exclusion Criteria:
-    1. If an alias symbol contains numerical characters not present in the primary gene symbol 
-    or official gene name, it should NOT be classified as an Alternate Abbreviation no matter what criteria it meets.
-    2. Aliases derived from historical protein names, molecular weights (e.g., numbers representing 
-    protein size), biochemical characterizations, or gene family names should NOT be considered Alternate Abbreviations.
-    Examples:
-    1-
-    Alias gene symbol: ACF65
-    Official HGNC gene name: APOBEC1 complementation factor
-    Primary gene symbol: A1CF
-    2-
-    Alias gene symbol: ALPHA4GNT
-    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
-    Primary gene symbol: A4GNT
+          <t xml:space="preserve">Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
+    You will get fired if your accuracy is less than 95%.
+    Background: An alternate abbreviation is when an alias symbol represents the same official gene name or the 
+    primary gene symbol but with different letters. If the alias symbol is representing a different description or a previous name of
+    the gene then it is not an alternate abbreviation. Be careful with alias symbols that seem to be shortened versions
+    of the primary gene symbol, they may be a family name and therefore not an alternate abbreviation. Alias symbols
+    have extra characters may be alternate abbreviations unless they have characters that are not present in the official 
+    gene name provided in the prompt. Keep in mind, a gene name with a number after the name is not the same gene as a gene name 
+    with no numbers or different numbers after the name.
+    Task: Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. Give a one sentence reason for
+    your determination.
+    Here is the gene information:
+    Alias gene symbol: ARTC5
+    HGNC record ID: HGNC:24049
+    Primary gene symbol: ART5
+    Official HGNC gene name: ADP-ribosyltransferase 5
     Rules:
     If the alias symbol is not an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -661,28 +636,28 @@
     Output (Strict):
     Output only one JSON object. No markdown.
     {
-    "hgnc_id":"HGNC:11540"
-    "alias_symbol": "TAF(II)80",
-    "primary_gene_symbol": "TAF6",
-    "name": "TATA-box binding protein associated factor 6",
+    "reason": statement,
     "alternate_abbreviation": "TRUE or FALSE"
-    }</t>
+    }
+    </t>
         </is>
       </c>
       <c r="I3" t="b">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>passed_filters</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>{
-    "hgnc_id": "HGNC:11540",
-    "alias_symbol": "TAF(II)80",
-    "primary_gene_symbol": "TAF6",
-    "name": "TATA-box binding protein associated factor 6",
-    "alternate_abbreviation": "FALSE"
+"reason": "ARTC5 is an alternate abbreviation of ADP-ribosyltransferase 5, as it includes the 'C' from 'ribosyltransferase' in addition to the primary symbol ART5.",
+"alternate_abbreviation": "TRUE"
 }</t>
         </is>
       </c>
@@ -690,32 +665,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HGNC:12474</t>
+          <t>HGNC:3308</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENSG00000072401</t>
+          <t>ENSG00000139610</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GENE ID:7321</t>
+          <t>GENE ID:1990</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UBE2D1</t>
+          <t>CELA1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UBCH5</t>
+          <t>ELA1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ubiquitin conjugating enzyme E2 D1</t>
+          <t>chymotrypsin like elastase 1</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -723,37 +698,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
-    Inputs:
-    Alias gene symbol: UBCH5
-    HGNC record ID: HGNC:12474
-    Primary gene symbol: UBE2D1
-    Official HGNC gene name: ubiquitin conjugating enzyme E2 D1
-    Task:
-    Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. 
-    Classify the alias symbol as an Alternate Abbreviation if it meets at least one of these criteria:
-    1. If the alias symbol letters expand directly to the words present in the official HGNC gene name
-    or a nearly identical wording, while still uniquely identifying the same gene. 
-    2. If the alias symbol differs from the primary gene symbol only by non-alphanumeric characters.
-    3. If the alias symbol has the same alphanumeric order as the primary gene symbol but is truncated 
-    through the removal of select characters. 
-    Special case: 
-    Alias symbols for microRNA genes that have the "hsa" or "HSA" prefix are not Alternate Abbreviations 
-    while those without the "hsa" or "HSA" prefix are Alternate Abbreviations.
-    Exclusion Criteria:
-    1. If an alias symbol contains numerical characters not present in the primary gene symbol 
-    or official gene name, it should NOT be classified as an Alternate Abbreviation no matter what criteria it meets.
-    2. Aliases derived from historical protein names, molecular weights (e.g., numbers representing 
-    protein size), biochemical characterizations, or gene family names should NOT be considered Alternate Abbreviations.
-    Examples:
-    1-
-    Alias gene symbol: ACF65
-    Official HGNC gene name: APOBEC1 complementation factor
-    Primary gene symbol: A1CF
-    2-
-    Alias gene symbol: ALPHA4GNT
-    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
-    Primary gene symbol: A4GNT
+          <t xml:space="preserve">Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
+    You will get fired if your accuracy is less than 95%.
+    Background: An alternate abbreviation is when an alias symbol represents the same official gene name or the 
+    primary gene symbol but with different letters. If the alias symbol is representing a different description or a previous name of
+    the gene then it is not an alternate abbreviation. Be careful with alias symbols that seem to be shortened versions
+    of the primary gene symbol, they may be a family name and therefore not an alternate abbreviation. Alias symbols
+    have extra characters may be alternate abbreviations unless they have characters that are not present in the official 
+    gene name provided in the prompt. Keep in mind, a gene name with a number after the name is not the same gene as a gene name 
+    with no numbers or different numbers after the name.
+    Task: Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. Give a one sentence reason for
+    your determination.
+    Here is the gene information:
+    Alias gene symbol: ELA1
+    HGNC record ID: HGNC:3308
+    Primary gene symbol: CELA1
+    Official HGNC gene name: chymotrypsin like elastase 1
     Rules:
     If the alias symbol is not an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -762,28 +722,28 @@
     Output (Strict):
     Output only one JSON object. No markdown.
     {
-    "hgnc_id":"HGNC:12474"
-    "alias_symbol": "UBCH5",
-    "primary_gene_symbol": "UBE2D1",
-    "name": "ubiquitin conjugating enzyme E2 D1",
+    "reason": statement,
     "alternate_abbreviation": "TRUE or FALSE"
-    }</t>
+    }
+    </t>
         </is>
       </c>
       <c r="I4" t="b">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>passed_filters</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>{
-    "hgnc_id": "HGNC:12474",
-    "alias_symbol": "UBCH5",
-    "primary_gene_symbol": "UBE2D1",
-    "name": "ubiquitin conjugating enzyme E2 D1",
-    "alternate_abbreviation": "FALSE"
+"reason": "ELA1 is an alternate abbreviation of the official gene name 'chymotrypsin like elastase 1' as it uses the first letter of 'elastase' and the number '1' from the full name.",
+"alternate_abbreviation": "TRUE"
 }</t>
         </is>
       </c>
@@ -791,32 +751,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HGNC:16046</t>
+          <t>HGNC:7406</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ENSG00000115446</t>
+          <t>ENSG00000125148</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GENE ID:25972</t>
+          <t>GENE ID:4502</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UNC50</t>
+          <t>MT2A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UNCL</t>
+          <t>MT-II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>unc-50 inner nuclear membrane RNA binding protein</t>
+          <t>metallothionein 2A</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -824,37 +784,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
-    Inputs:
-    Alias gene symbol: UNCL
-    HGNC record ID: HGNC:16046
-    Primary gene symbol: UNC50
-    Official HGNC gene name: unc-50 inner nuclear membrane RNA binding protein
-    Task:
-    Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. 
-    Classify the alias symbol as an Alternate Abbreviation if it meets at least one of these criteria:
-    1. If the alias symbol letters expand directly to the words present in the official HGNC gene name
-    or a nearly identical wording, while still uniquely identifying the same gene. 
-    2. If the alias symbol differs from the primary gene symbol only by non-alphanumeric characters.
-    3. If the alias symbol has the same alphanumeric order as the primary gene symbol but is truncated 
-    through the removal of select characters. 
-    Special case: 
-    Alias symbols for microRNA genes that have the "hsa" or "HSA" prefix are not Alternate Abbreviations 
-    while those without the "hsa" or "HSA" prefix are Alternate Abbreviations.
-    Exclusion Criteria:
-    1. If an alias symbol contains numerical characters not present in the primary gene symbol 
-    or official gene name, it should NOT be classified as an Alternate Abbreviation no matter what criteria it meets.
-    2. Aliases derived from historical protein names, molecular weights (e.g., numbers representing 
-    protein size), biochemical characterizations, or gene family names should NOT be considered Alternate Abbreviations.
-    Examples:
-    1-
-    Alias gene symbol: ACF65
-    Official HGNC gene name: APOBEC1 complementation factor
-    Primary gene symbol: A1CF
-    2-
-    Alias gene symbol: ALPHA4GNT
-    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
-    Primary gene symbol: A4GNT
+          <t xml:space="preserve">Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
+    You will get fired if your accuracy is less than 95%.
+    Background: An alternate abbreviation is when an alias symbol represents the same official gene name or the 
+    primary gene symbol but with different letters. If the alias symbol is representing a different description or a previous name of
+    the gene then it is not an alternate abbreviation. Be careful with alias symbols that seem to be shortened versions
+    of the primary gene symbol, they may be a family name and therefore not an alternate abbreviation. Alias symbols
+    have extra characters may be alternate abbreviations unless they have characters that are not present in the official 
+    gene name provided in the prompt. Keep in mind, a gene name with a number after the name is not the same gene as a gene name 
+    with no numbers or different numbers after the name.
+    Task: Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. Give a one sentence reason for
+    your determination.
+    Here is the gene information:
+    Alias gene symbol: MT-II
+    HGNC record ID: HGNC:7406
+    Primary gene symbol: MT2A
+    Official HGNC gene name: metallothionein 2A
     Rules:
     If the alias symbol is not an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -863,27 +808,27 @@
     Output (Strict):
     Output only one JSON object. No markdown.
     {
-    "hgnc_id":"HGNC:16046"
-    "alias_symbol": "UNCL",
-    "primary_gene_symbol": "UNC50",
-    "name": "unc-50 inner nuclear membrane RNA binding protein",
+    "reason": statement,
     "alternate_abbreviation": "TRUE or FALSE"
-    }</t>
+    }
+    </t>
         </is>
       </c>
       <c r="I5" t="b">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>passed_filters</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>{
-"hgnc_id":"HGNC:16046",
-"alias_symbol": "UNCL",
-"primary_gene_symbol": "UNC50",
-"name": "unc-50 inner nuclear membrane RNA binding protein",
+"reason": "MT-II is an alternate abbreviation of metallothionein 2A, as it uses different letters to represent the same gene name.",
 "alternate_abbreviation": "TRUE"
 }</t>
         </is>
@@ -892,32 +837,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HGNC:18949</t>
+          <t>HGNC:9969</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ENSG00000227840</t>
+          <t>ENSG00000035928</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GENE ID:337981</t>
+          <t>GENE ID:5981</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KRTAP8-3P</t>
+          <t>RFC1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRTAP8P2</t>
+          <t>RECC1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>keratin associated protein 8-3, pseudogene</t>
+          <t>replication factor C subunit 1</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -925,37 +870,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
-    Inputs:
-    Alias gene symbol: KRTAP8P2
-    HGNC record ID: HGNC:18949
-    Primary gene symbol: KRTAP8-3P
-    Official HGNC gene name: keratin associated protein 8-3, pseudogene
-    Task:
-    Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. 
-    Classify the alias symbol as an Alternate Abbreviation if it meets at least one of these criteria:
-    1. If the alias symbol letters expand directly to the words present in the official HGNC gene name
-    or a nearly identical wording, while still uniquely identifying the same gene. 
-    2. If the alias symbol differs from the primary gene symbol only by non-alphanumeric characters.
-    3. If the alias symbol has the same alphanumeric order as the primary gene symbol but is truncated 
-    through the removal of select characters. 
-    Special case: 
-    Alias symbols for microRNA genes that have the "hsa" or "HSA" prefix are not Alternate Abbreviations 
-    while those without the "hsa" or "HSA" prefix are Alternate Abbreviations.
-    Exclusion Criteria:
-    1. If an alias symbol contains numerical characters not present in the primary gene symbol 
-    or official gene name, it should NOT be classified as an Alternate Abbreviation no matter what criteria it meets.
-    2. Aliases derived from historical protein names, molecular weights (e.g., numbers representing 
-    protein size), biochemical characterizations, or gene family names should NOT be considered Alternate Abbreviations.
-    Examples:
-    1-
-    Alias gene symbol: ACF65
-    Official HGNC gene name: APOBEC1 complementation factor
-    Primary gene symbol: A1CF
-    2-
-    Alias gene symbol: ALPHA4GNT
-    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
-    Primary gene symbol: A4GNT
+          <t xml:space="preserve">Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
+    You will get fired if your accuracy is less than 95%.
+    Background: An alternate abbreviation is when an alias symbol represents the same official gene name or the 
+    primary gene symbol but with different letters. If the alias symbol is representing a different description or a previous name of
+    the gene then it is not an alternate abbreviation. Be careful with alias symbols that seem to be shortened versions
+    of the primary gene symbol, they may be a family name and therefore not an alternate abbreviation. Alias symbols
+    have extra characters may be alternate abbreviations unless they have characters that are not present in the official 
+    gene name provided in the prompt. Keep in mind, a gene name with a number after the name is not the same gene as a gene name 
+    with no numbers or different numbers after the name.
+    Task: Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. Give a one sentence reason for
+    your determination.
+    Here is the gene information:
+    Alias gene symbol: RECC1
+    HGNC record ID: HGNC:9969
+    Primary gene symbol: RFC1
+    Official HGNC gene name: replication factor C subunit 1
     Rules:
     If the alias symbol is not an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -964,230 +894,28 @@
     Output (Strict):
     Output only one JSON object. No markdown.
     {
-    "hgnc_id":"HGNC:18949"
-    "alias_symbol": "KRTAP8P2",
-    "primary_gene_symbol": "KRTAP8-3P",
-    "name": "keratin associated protein 8-3, pseudogene",
+    "reason": statement,
     "alternate_abbreviation": "TRUE or FALSE"
-    }</t>
+    }
+    </t>
         </is>
       </c>
       <c r="I6" t="b">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0.875</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>passed_filters</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>{
-    "hgnc_id": "HGNC:18949",
-    "alias_symbol": "KRTAP8P2",
-    "primary_gene_symbol": "KRTAP8-3P",
-    "name": "keratin associated protein 8-3, pseudogene",
-    "alternate_abbreviation": "TRUE"
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HGNC:19</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ENSG00000129673</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GENE ID:15</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>AANAT</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SNAT</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>aralkylamine N-acetyltransferase</t>
-        </is>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
-    Inputs:
-    Alias gene symbol: SNAT
-    HGNC record ID: HGNC:19
-    Primary gene symbol: AANAT
-    Official HGNC gene name: aralkylamine N-acetyltransferase
-    Task:
-    Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. 
-    Classify the alias symbol as an Alternate Abbreviation if it meets at least one of these criteria:
-    1. If the alias symbol letters expand directly to the words present in the official HGNC gene name
-    or a nearly identical wording, while still uniquely identifying the same gene. 
-    2. If the alias symbol differs from the primary gene symbol only by non-alphanumeric characters.
-    3. If the alias symbol has the same alphanumeric order as the primary gene symbol but is truncated 
-    through the removal of select characters. 
-    Special case: 
-    Alias symbols for microRNA genes that have the "hsa" or "HSA" prefix are not Alternate Abbreviations 
-    while those without the "hsa" or "HSA" prefix are Alternate Abbreviations.
-    Exclusion Criteria:
-    1. If an alias symbol contains numerical characters not present in the primary gene symbol 
-    or official gene name, it should NOT be classified as an Alternate Abbreviation no matter what criteria it meets.
-    2. Aliases derived from historical protein names, molecular weights (e.g., numbers representing 
-    protein size), biochemical characterizations, or gene family names should NOT be considered Alternate Abbreviations.
-    Examples:
-    1-
-    Alias gene symbol: ACF65
-    Official HGNC gene name: APOBEC1 complementation factor
-    Primary gene symbol: A1CF
-    2-
-    Alias gene symbol: ALPHA4GNT
-    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
-    Primary gene symbol: A4GNT
-    Rules:
-    If the alias symbol is not an alternate abbreviation, return:
-    "alternate_abbreviation": "FALSE"
-    If the alias symbol is an alternate abbreviation, return:
-    "alternate_abbreviation": "TRUE"
-    Output (Strict):
-    Output only one JSON object. No markdown.
-    {
-    "hgnc_id":"HGNC:19"
-    "alias_symbol": "SNAT",
-    "primary_gene_symbol": "AANAT",
-    "name": "aralkylamine N-acetyltransferase",
-    "alternate_abbreviation": "TRUE or FALSE"
-    }</t>
-        </is>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>{
-    "hgnc_id": "HGNC:19",
-    "alias_symbol": "SNAT",
-    "primary_gene_symbol": "AANAT",
-    "name": "aralkylamine N-acetyltransferase",
-    "alternate_abbreviation": "TRUE"
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HGNC:6345</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ENSG00000105610</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GENE ID:10661</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>KLF1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>EKLF/KLF1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KLF transcription factor 1</t>
-        </is>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Role:You are a biomedical gene nomenclature curator trained in HGNC gene identity and alias symbol resolution.
-    Inputs:
-    Alias gene symbol: EKLF/KLF1
-    HGNC record ID: HGNC:6345
-    Primary gene symbol: KLF1
-    Official HGNC gene name: KLF transcription factor 1
-    Task:
-    Determine whether the alias symbol is an abbreviation variant of the official HGNC gene name. 
-    Classify the alias symbol as an Alternate Abbreviation if it meets at least one of these criteria:
-    1. If the alias symbol letters expand directly to the words present in the official HGNC gene name
-    or a nearly identical wording, while still uniquely identifying the same gene. 
-    2. If the alias symbol differs from the primary gene symbol only by non-alphanumeric characters.
-    3. If the alias symbol has the same alphanumeric order as the primary gene symbol but is truncated 
-    through the removal of select characters. 
-    Special case: 
-    Alias symbols for microRNA genes that have the "hsa" or "HSA" prefix are not Alternate Abbreviations 
-    while those without the "hsa" or "HSA" prefix are Alternate Abbreviations.
-    Exclusion Criteria:
-    1. If an alias symbol contains numerical characters not present in the primary gene symbol 
-    or official gene name, it should NOT be classified as an Alternate Abbreviation no matter what criteria it meets.
-    2. Aliases derived from historical protein names, molecular weights (e.g., numbers representing 
-    protein size), biochemical characterizations, or gene family names should NOT be considered Alternate Abbreviations.
-    Examples:
-    1-
-    Alias gene symbol: ACF65
-    Official HGNC gene name: APOBEC1 complementation factor
-    Primary gene symbol: A1CF
-    2-
-    Alias gene symbol: ALPHA4GNT
-    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
-    Primary gene symbol: A4GNT
-    Rules:
-    If the alias symbol is not an alternate abbreviation, return:
-    "alternate_abbreviation": "FALSE"
-    If the alias symbol is an alternate abbreviation, return:
-    "alternate_abbreviation": "TRUE"
-    Output (Strict):
-    Output only one JSON object. No markdown.
-    {
-    "hgnc_id":"HGNC:6345"
-    "alias_symbol": "EKLF/KLF1",
-    "primary_gene_symbol": "KLF1",
-    "name": "KLF transcription factor 1",
-    "alternate_abbreviation": "TRUE or FALSE"
-    }</t>
-        </is>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>{
-    "hgnc_id": "HGNC:6345",
-    "alias_symbol": "EKLF/KLF1",
-    "primary_gene_symbol": "KLF1",
-    "name": "KLF transcription factor 1",
-    "alternate_abbreviation": "TRUE"
+"reason": "RECC1 is not an alternate abbreviation of 'replication factor C subunit 1' as it contains a 'C' not present in the official gene name.",
+"alternate_abbreviation": "FALSE"
 }</t>
         </is>
       </c>
